--- a/articles.xlsx
+++ b/articles.xlsx
@@ -33,9 +33,6 @@
     <t>Le Mexique lance sa Coupe du Monde</t>
   </si>
   <si>
-    <t>le mexique lance parfaitement.html</t>
-  </si>
-  <si>
     <t>Denis prend la tête du championnat</t>
   </si>
   <si>
@@ -46,6 +43,9 @@
   </si>
   <si>
     <t>Présentation du tournoi</t>
+  </si>
+  <si>
+    <t>le mexique lance parfaitement son mondial.html</t>
   </si>
 </sst>
 </file>
@@ -388,7 +388,8 @@
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -405,7 +406,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="75">
+    <row r="2" spans="1:4" ht="60">
       <c r="A2" s="1">
         <v>46185</v>
       </c>
@@ -413,10 +414,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60">
@@ -424,13 +425,13 @@
         <v>46184</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Date</t>
   </si>
@@ -46,6 +46,12 @@
   </si>
   <si>
     <t>le mexique lance parfaitement son mondial.html</t>
+  </si>
+  <si>
+    <t>les USA lance parfaitement leur mondial.html</t>
+  </si>
+  <si>
+    <t>Les USA lancent leur mondial</t>
   </si>
 </sst>
 </file>
@@ -81,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -89,6 +95,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,11 +390,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
     <col min="3" max="3" width="38.7109375" customWidth="1"/>
     <col min="4" max="4" width="32.28515625" customWidth="1"/>
   </cols>
@@ -432,6 +439,20 @@
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3">
+        <v>46186</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Date</t>
   </si>
@@ -52,6 +52,15 @@
   </si>
   <si>
     <t>Les USA lancent leur mondial</t>
+  </si>
+  <si>
+    <t>Matthias arrive à la redaction</t>
+  </si>
+  <si>
+    <t>Matthias revient sur ce premier choc de la coupe du monde</t>
+  </si>
+  <si>
+    <t>Le choc Bresil Maroc.html</t>
   </si>
 </sst>
 </file>
@@ -390,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -413,7 +422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="60">
+    <row r="2" spans="1:4" ht="30">
       <c r="A2" s="1">
         <v>46185</v>
       </c>
@@ -427,7 +436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="60">
+    <row r="3" spans="1:4" ht="30">
       <c r="A3" s="1">
         <v>46184</v>
       </c>
@@ -453,6 +462,20 @@
       </c>
       <c r="D4" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -60,7 +60,7 @@
     <t>Matthias revient sur ce premier choc de la coupe du monde</t>
   </si>
   <si>
-    <t>Le choc Bresil Maroc.html</t>
+    <t>le choc Bresil Maroc.html</t>
   </si>
 </sst>
 </file>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -61,6 +61,42 @@
   </si>
   <si>
     <t>le choc Bresil Maroc.html</t>
+  </si>
+  <si>
+    <t>Un dernier avant le hellfest</t>
+  </si>
+  <si>
+    <t>un dernier avant le hellfest.html</t>
+  </si>
+  <si>
+    <t>Arnaud le visionnaire et moi au hellfest</t>
+  </si>
+  <si>
+    <t>Matthias à le spleen</t>
+  </si>
+  <si>
+    <t>matthias à le spleen.html</t>
+  </si>
+  <si>
+    <t>Matthias, baudelaire et MPP</t>
+  </si>
+  <si>
+    <t>matthias vieilli</t>
+  </si>
+  <si>
+    <t>matthias vieilli.html</t>
+  </si>
+  <si>
+    <t>Matthias, ronaldo et le Goat</t>
+  </si>
+  <si>
+    <t>De retour</t>
+  </si>
+  <si>
+    <t>De retour à la redac.html</t>
+  </si>
+  <si>
+    <t>Hellfest et troisieme journée</t>
   </si>
 </sst>
 </file>
@@ -399,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -478,6 +514,62 @@
         <v>13</v>
       </c>
     </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3">
+        <v>46191</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3">
+        <v>46198</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -97,6 +97,33 @@
   </si>
   <si>
     <t>Hellfest et troisieme journée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debut des seiziemes </t>
+  </si>
+  <si>
+    <t>debut des seiziemes.html</t>
+  </si>
+  <si>
+    <t>Le canada lance les 1/16</t>
+  </si>
+  <si>
+    <t>Matthias et ses hallucinations</t>
+  </si>
+  <si>
+    <t>Matthias et ses hallucinations.html</t>
+  </si>
+  <si>
+    <t>Le maroc au bout du suspence</t>
+  </si>
+  <si>
+    <t>La France convaincante</t>
+  </si>
+  <si>
+    <t>La France convaincante.html</t>
+  </si>
+  <si>
+    <t>La France impressionne pour le début des seiziemes</t>
   </si>
 </sst>
 </file>
@@ -435,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -568,6 +595,48 @@
       </c>
       <c r="D9" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>Date</t>
   </si>
@@ -124,6 +124,15 @@
   </si>
   <si>
     <t>La France impressionne pour le début des seiziemes</t>
+  </si>
+  <si>
+    <t>King Harry</t>
+  </si>
+  <si>
+    <t>King Harry.html</t>
+  </si>
+  <si>
+    <t>L'angleterre et la Belgique au bout du suspence</t>
   </si>
 </sst>
 </file>
@@ -462,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -637,6 +646,20 @@
       </c>
       <c r="D12" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3">
+        <v>46205</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Date</t>
   </si>
@@ -133,6 +133,24 @@
   </si>
   <si>
     <t>L'angleterre et la Belgique au bout du suspence</t>
+  </si>
+  <si>
+    <t>La France et le maroc sans convaincre</t>
+  </si>
+  <si>
+    <t>La France et le maroc sans convaincre.html</t>
+  </si>
+  <si>
+    <t>Le maroc et la France se retrouveront en quart</t>
+  </si>
+  <si>
+    <t>Le bresil conquis par le roi de norvege</t>
+  </si>
+  <si>
+    <t>Le bresil conquis par le roi de norvege.html</t>
+  </si>
+  <si>
+    <t>La norvege et l'angleterre en quart</t>
   </si>
 </sst>
 </file>
@@ -471,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -660,6 +678,34 @@
       </c>
       <c r="D13" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3">
+        <v>46208</v>
+      </c>
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="3">
+        <v>46209</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>Date</t>
   </si>
@@ -151,6 +151,24 @@
   </si>
   <si>
     <t>La norvege et l'angleterre en quart</t>
+  </si>
+  <si>
+    <t>Ronaldo à la retraite</t>
+  </si>
+  <si>
+    <t>Ronaldo à la retraite.html</t>
+  </si>
+  <si>
+    <t>Le karma rattrape les USA</t>
+  </si>
+  <si>
+    <t>Messi est eternel</t>
+  </si>
+  <si>
+    <t>Messi est eternel.html</t>
+  </si>
+  <si>
+    <t>L'argentine au bout du suspence</t>
   </si>
 </sst>
 </file>
@@ -489,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -706,6 +724,34 @@
       </c>
       <c r="D15" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3">
+        <v>46210</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="3">
+        <v>46242</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
     <t>Date</t>
   </si>
@@ -169,6 +169,15 @@
   </si>
   <si>
     <t>L'argentine au bout du suspence</t>
+  </si>
+  <si>
+    <t>France- Maroc</t>
+  </si>
+  <si>
+    <t>France- Maroc.html</t>
+  </si>
+  <si>
+    <t>Lancement des quarts de finale</t>
   </si>
 </sst>
 </file>
@@ -507,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -742,7 +751,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3">
-        <v>46242</v>
+        <v>46211</v>
       </c>
       <c r="B17" t="s">
         <v>48</v>
@@ -752,6 +761,20 @@
       </c>
       <c r="D17" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3">
+        <v>46212</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>Date</t>
   </si>
@@ -178,6 +178,33 @@
   </si>
   <si>
     <t>Lancement des quarts de finale</t>
+  </si>
+  <si>
+    <t>La France en demi</t>
+  </si>
+  <si>
+    <t>La France en demi.html</t>
+  </si>
+  <si>
+    <t>le maroc pas au rendez vous</t>
+  </si>
+  <si>
+    <t>L'Espagne au rendez vous des demi</t>
+  </si>
+  <si>
+    <t>L'Espagne au rendez vous des demi.html</t>
+  </si>
+  <si>
+    <t>Merino le hero espagnol</t>
+  </si>
+  <si>
+    <t>L'angleterre repouse les vikings</t>
+  </si>
+  <si>
+    <t>L'angleterre repouse les vikings.html</t>
+  </si>
+  <si>
+    <t>l'argentine toujours favorisé</t>
   </si>
 </sst>
 </file>
@@ -516,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -775,6 +802,48 @@
       </c>
       <c r="D18" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3">
+        <v>46214</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/articles.xlsx
+++ b/articles.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -205,6 +205,24 @@
   </si>
   <si>
     <t>l'argentine toujours favorisé</t>
+  </si>
+  <si>
+    <t>La France pas à la fete</t>
+  </si>
+  <si>
+    <t>La France pas à la fete.html</t>
+  </si>
+  <si>
+    <t>L'Espagne était trop forte</t>
+  </si>
+  <si>
+    <t>L'argentine est invincible</t>
+  </si>
+  <si>
+    <t>L'argentine est invincible.html</t>
+  </si>
+  <si>
+    <t>L'angleterre is coming home</t>
   </si>
 </sst>
 </file>
@@ -543,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -844,6 +862,34 @@
       </c>
       <c r="D21" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
